--- a/DateBase/orders/Nha Thu_2026-7-15.xlsx
+++ b/DateBase/orders/Nha Thu_2026-7-15.xlsx
@@ -1112,6 +1112,9 @@
       <c r="G2" t="str">
         <v>0401051141010710761016881071051010532510102010101012520303010101010555555555515851051010101051055510101020201051010</v>
       </c>
+      <c r="H2" t="str">
+        <v>CNY</v>
+      </c>
     </row>
   </sheetData>
   <ignoredErrors>
